--- a/Test-Cases-Submission.xlsx
+++ b/Test-Cases-Submission.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\doda_\OneDrive - St. Lawrence College\_SLC\Winter25\QUAL2000\Week-10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2db921fd99e4e5bb/Documents/St-Lawrence-College/SLC/20252026/Semester 2/QualityAssurance/Final Project/Testing/QUAL2000-Event-Hub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5BAACD-E979-4F94-BEA8-B5AD4B6F2AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="316" documentId="13_ncr:1_{CC5BAACD-E979-4F94-BEA8-B5AD4B6F2AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6DA6DB5-4A19-47EC-9F16-70503D0D2438}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="100">
   <si>
     <t>Test ID</t>
   </si>
@@ -57,9 +57,6 @@
     <t>Landing Page appears</t>
   </si>
   <si>
-    <t>E2E Testing with Playwright</t>
-  </si>
-  <si>
     <t>Execution Status (Pass/Fail)</t>
   </si>
   <si>
@@ -69,29 +66,272 @@
     <t>Bug Priority(Low/Medium/High)</t>
   </si>
   <si>
-    <t>1001-Example</t>
-  </si>
-  <si>
-    <t>This is an example test case</t>
-  </si>
-  <si>
-    <t>1002-Example</t>
-  </si>
-  <si>
-    <t>Click on the button with the text "Enter"</t>
-  </si>
-  <si>
     <t>Click</t>
   </si>
   <si>
-    <t>The movies page appears</t>
+    <t xml:space="preserve">E2E Testing with JS Testing </t>
+  </si>
+  <si>
+    <t>1001-Home</t>
+  </si>
+  <si>
+    <t>1002-Home</t>
+  </si>
+  <si>
+    <t>1003-Home</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "Events" in nav</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "Home" in nav</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "Log In" in nav</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "Register" in nav</t>
+  </si>
+  <si>
+    <t>The Home page appears</t>
+  </si>
+  <si>
+    <t>The Events page appears</t>
+  </si>
+  <si>
+    <t>The Log In page appears</t>
+  </si>
+  <si>
+    <t>The Register page appears</t>
+  </si>
+  <si>
+    <t>1004-Home</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "Create Account" in nav</t>
+  </si>
+  <si>
+    <t>The Admin Login Page appears</t>
+  </si>
+  <si>
+    <t>0001-DevEnvironment</t>
+  </si>
+  <si>
+    <t>Click on logo in nav</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "Browse Events"</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "Create Your Accounts"</t>
+  </si>
+  <si>
+    <t>The associated event page appears</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "See All Events"</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "Log In To Manage Events"</t>
+  </si>
+  <si>
+    <t>Event Page Section</t>
+  </si>
+  <si>
+    <t>Developer Section</t>
+  </si>
+  <si>
+    <t>Home Page Section</t>
+  </si>
+  <si>
+    <t>2001-Events</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "Admin Dashboard" in nav</t>
+  </si>
+  <si>
+    <t>Be logged out and click specific event</t>
+  </si>
+  <si>
+    <t>Be logged in and click specific event</t>
+  </si>
+  <si>
+    <t>Specific Event Section</t>
+  </si>
+  <si>
+    <t>2002-Events</t>
+  </si>
+  <si>
+    <t>2003-Events</t>
+  </si>
+  <si>
+    <t>2004-Events</t>
+  </si>
+  <si>
+    <t>2005-Events</t>
+  </si>
+  <si>
+    <t>2006-Events</t>
+  </si>
+  <si>
+    <t>2007-Events</t>
+  </si>
+  <si>
+    <t>2008-Events</t>
+  </si>
+  <si>
+    <t>3001-SpEvents</t>
+  </si>
+  <si>
+    <t>3002-SpEvents</t>
+  </si>
+  <si>
+    <t>LOG IN</t>
+  </si>
+  <si>
+    <t>LOG OUT</t>
+  </si>
+  <si>
+    <t>"Register For This Event" button appears on page</t>
+  </si>
+  <si>
+    <t>"Log In To Register" button appears on page</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "Log In To Register"</t>
+  </si>
+  <si>
+    <t>Login page appears</t>
+  </si>
+  <si>
+    <t>3003-SpEvents</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "Create Account"</t>
+  </si>
+  <si>
+    <t>Register page appears</t>
+  </si>
+  <si>
+    <t>3004-SpEvents</t>
+  </si>
+  <si>
+    <t>Events page appears</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click on the button with the text "Back To Events" </t>
+  </si>
+  <si>
+    <t>Click on the button with the text "View My Events"</t>
+  </si>
+  <si>
+    <t>My Events page appears</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "Register For This Event"</t>
+  </si>
+  <si>
+    <t>Register for event page appears</t>
+  </si>
+  <si>
+    <t>3005-SpEvents</t>
+  </si>
+  <si>
+    <t>3006-SpEvents</t>
+  </si>
+  <si>
+    <t>3007-SpEvents</t>
+  </si>
+  <si>
+    <t>3008-SpEvents</t>
+  </si>
+  <si>
+    <t>Click on event carousel</t>
+  </si>
+  <si>
+    <t>Navigation Section</t>
+  </si>
+  <si>
+    <t>0010-Nav</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "My Events" in nav</t>
+  </si>
+  <si>
+    <t>The My Events page appears</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "My Calendar" in nav</t>
+  </si>
+  <si>
+    <t>The My Calendar page appears</t>
+  </si>
+  <si>
+    <t>Click on the button with the text "Log Out" in nav</t>
+  </si>
+  <si>
+    <t>View username</t>
+  </si>
+  <si>
+    <t>The user's Username is displayed</t>
+  </si>
+  <si>
+    <t>Go to https://github.com/JeffBolk/QUAL2000-Event-Hub</t>
+  </si>
+  <si>
+    <t>GitHub Actions passed</t>
+  </si>
+  <si>
+    <t>Register User Section</t>
+  </si>
+  <si>
+    <t>4001-RegisterUser</t>
+  </si>
+  <si>
+    <t>Keep fields blank and click on button with text "create account"</t>
+  </si>
+  <si>
+    <t>Button disabled and informs user to input information</t>
+  </si>
+  <si>
+    <t>4002-RegisterUser</t>
+  </si>
+  <si>
+    <t>Enter "Jeffrey Bolk" in text field "Full Name" and enter "abcd" in "Email" field and click on button with text "create account"</t>
+  </si>
+  <si>
+    <t>Text Input and Button Click</t>
+  </si>
+  <si>
+    <t>Button disabled and informs user to input valid email address</t>
+  </si>
+  <si>
+    <t>Button disabled</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Inform user of incorrect input</t>
+  </si>
+  <si>
+    <t>4003-RegisterUser</t>
+  </si>
+  <si>
+    <t>Enter "Jeffrey Bolk" in text field "Full Name" and enter "jeffrey.bolk@Student.SL.On.Ca" in "Email" field and "password" in "Password" field click on button with text "create account"</t>
+  </si>
+  <si>
+    <t>Account created and My Events page appears</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,8 +339,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -113,8 +367,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -122,19 +382,111 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7575"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF7575"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -409,26 +761,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J54"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21.36328125" customWidth="1"/>
-    <col min="2" max="2" width="38.08984375" customWidth="1"/>
-    <col min="3" max="3" width="41.6328125" customWidth="1"/>
-    <col min="4" max="4" width="20.453125" customWidth="1"/>
-    <col min="5" max="5" width="21.08984375" customWidth="1"/>
-    <col min="6" max="6" width="29.453125" customWidth="1"/>
-    <col min="7" max="7" width="34.1796875" customWidth="1"/>
-    <col min="8" max="8" width="35.08984375" customWidth="1"/>
-    <col min="9" max="9" width="34.90625" customWidth="1"/>
-    <col min="10" max="10" width="48.26953125" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" customWidth="1"/>
+    <col min="2" max="2" width="40.53125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="41.59765625" customWidth="1"/>
+    <col min="4" max="4" width="33.46484375" customWidth="1"/>
+    <col min="5" max="5" width="33.59765625" customWidth="1"/>
+    <col min="6" max="6" width="29.46484375" customWidth="1"/>
+    <col min="7" max="7" width="34.19921875" customWidth="1"/>
+    <col min="8" max="8" width="35.06640625" customWidth="1"/>
+    <col min="9" max="9" width="34.9296875" customWidth="1"/>
+    <col min="10" max="10" width="48.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -444,56 +796,889 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+    </row>
+    <row r="3" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="14"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="D22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A23" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B26" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A39" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A40" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="14"/>
+    </row>
+    <row r="41" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>63</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A46" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="12"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="14"/>
+    </row>
+    <row r="47" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>71</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A51" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+    </row>
+    <row r="52" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>90</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C53" t="s">
+        <v>92</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H53" t="s">
+        <v>95</v>
+      </c>
+      <c r="I53" t="s">
+        <v>95</v>
+      </c>
+      <c r="J53" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="57" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C54" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" display="Go to repo and verify Gituib Actions https://github.com/JeffBolk/QUAL2000-Event-Hub" xr:uid="{32518946-939D-4B73-A67D-34E6923DA913}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Test-Cases-Submission.xlsx
+++ b/Test-Cases-Submission.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2db921fd99e4e5bb/Documents/St-Lawrence-College/SLC/20252026/Semester 2/QualityAssurance/Final Project/Testing/QUAL2000-Event-Hub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="316" documentId="13_ncr:1_{CC5BAACD-E979-4F94-BEA8-B5AD4B6F2AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6DA6DB5-4A19-47EC-9F16-70503D0D2438}"/>
+  <xr:revisionPtr revIDLastSave="585" documentId="13_ncr:1_{CC5BAACD-E979-4F94-BEA8-B5AD4B6F2AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0AE8994-4420-4CAB-90CC-4432C7024034}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="180">
   <si>
     <t>Test ID</t>
   </si>
@@ -255,9 +255,6 @@
     <t>Navigation Section</t>
   </si>
   <si>
-    <t>0010-Nav</t>
-  </si>
-  <si>
     <t>Click on the button with the text "My Events" in nav</t>
   </si>
   <si>
@@ -303,9 +300,6 @@
     <t>Enter "Jeffrey Bolk" in text field "Full Name" and enter "abcd" in "Email" field and click on button with text "create account"</t>
   </si>
   <si>
-    <t>Text Input and Button Click</t>
-  </si>
-  <si>
     <t>Button disabled and informs user to input valid email address</t>
   </si>
   <si>
@@ -325,6 +319,252 @@
   </si>
   <si>
     <t>Account created and My Events page appears</t>
+  </si>
+  <si>
+    <t>Login User Section</t>
+  </si>
+  <si>
+    <t>5001-LoginUser</t>
+  </si>
+  <si>
+    <t>5002-LoginUser</t>
+  </si>
+  <si>
+    <t>5003-LoginUser</t>
+  </si>
+  <si>
+    <t>Enter "password" in text field "password" and enter "abcd" in "Email" field and click on button with text "Log In"</t>
+  </si>
+  <si>
+    <t>Keep fields blank and click on button with text "Log In"</t>
+  </si>
+  <si>
+    <t>Enter "jeffrey.bolk@Student.SL.On.Ca" in "Email" field and "password" in "Password" field click on button with text "Log In"</t>
+  </si>
+  <si>
+    <t>Logged in and My Events page appears</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>6001-RegisterEvent</t>
+  </si>
+  <si>
+    <t>Register Event Section</t>
+  </si>
+  <si>
+    <t>Add two seats and submit form using "Add To My Calendar" button</t>
+  </si>
+  <si>
+    <t>Text input and Click</t>
+  </si>
+  <si>
+    <t>Update event registration by clicking "Update My Seats" and changing seat count to 10</t>
+  </si>
+  <si>
+    <t>Event updated in My Events, My Calendar and event seat count decreased in event</t>
+  </si>
+  <si>
+    <t>Event added in My Events, My Calendar and event seat count decreased in event</t>
+  </si>
+  <si>
+    <t>6002-RegisterEvent</t>
+  </si>
+  <si>
+    <t>6003-RegisterEvent</t>
+  </si>
+  <si>
+    <t>Delete Event from My Events</t>
+  </si>
+  <si>
+    <t>Event deleted in My Events, My Calendar and event seat count increased in event</t>
+  </si>
+  <si>
+    <t>Text Input and Click</t>
+  </si>
+  <si>
+    <t>My Calendar Section</t>
+  </si>
+  <si>
+    <t>7003-Calendar</t>
+  </si>
+  <si>
+    <t>Click button with text "Next Month"</t>
+  </si>
+  <si>
+    <t>Click button with text "Current Month"</t>
+  </si>
+  <si>
+    <t>Click button with text "Previous Month"</t>
+  </si>
+  <si>
+    <t>7001-Calendar</t>
+  </si>
+  <si>
+    <t>7002-Calendar</t>
+  </si>
+  <si>
+    <t>Calendar changed to next month</t>
+  </si>
+  <si>
+    <t>Calendar changed to current month</t>
+  </si>
+  <si>
+    <t>Calendar changed to previous month</t>
+  </si>
+  <si>
+    <t>Admin Dashboard Section</t>
+  </si>
+  <si>
+    <t>8001-Dashboard</t>
+  </si>
+  <si>
+    <t>Use credential to populate text fields and sign in</t>
+  </si>
+  <si>
+    <t>Click button with text "Return To Public Site"</t>
+  </si>
+  <si>
+    <t>Consider reroute to home page instead</t>
+  </si>
+  <si>
+    <t>All Events page appears</t>
+  </si>
+  <si>
+    <t>EDIT ADMIN EVENTS</t>
+  </si>
+  <si>
+    <t>8002-Dashboard</t>
+  </si>
+  <si>
+    <t>8003-Dashboard</t>
+  </si>
+  <si>
+    <t>Add new event with correct inputs</t>
+  </si>
+  <si>
+    <t>Event Added in Events</t>
+  </si>
+  <si>
+    <t>6004-RegisterEvent</t>
+  </si>
+  <si>
+    <t>Register for event that is passed</t>
+  </si>
+  <si>
+    <t>Will not allow user to register for past events</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Do not let users register for past events</t>
+  </si>
+  <si>
+    <t>8004-Dashboard</t>
+  </si>
+  <si>
+    <t>Event Removed from Events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete Event from All Events using delete button </t>
+  </si>
+  <si>
+    <t>8005-Dashboard</t>
+  </si>
+  <si>
+    <t>Edit Event using edit button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete Event from All Events when user is registered using delete button </t>
+  </si>
+  <si>
+    <t>Edit Event when user is registered using edit button</t>
+  </si>
+  <si>
+    <t>Event Removed from My Events and Calendar</t>
+  </si>
+  <si>
+    <t>8006-Dashboard</t>
+  </si>
+  <si>
+    <t>Click button with text "View Public Site"</t>
+  </si>
+  <si>
+    <t>Public Site appears</t>
+  </si>
+  <si>
+    <t>8007-Dashboard</t>
+  </si>
+  <si>
+    <t>Click button with text "Log Out"</t>
+  </si>
+  <si>
+    <t>Admin Logged out and admin login page appears</t>
+  </si>
+  <si>
+    <t>0011-Nav</t>
+  </si>
+  <si>
+    <t>0012-Nav</t>
+  </si>
+  <si>
+    <t>0013-Nav</t>
+  </si>
+  <si>
+    <t>0014-Nav</t>
+  </si>
+  <si>
+    <t>0015-Nav</t>
+  </si>
+  <si>
+    <t>0016-Nav</t>
+  </si>
+  <si>
+    <t>0017-Nav</t>
+  </si>
+  <si>
+    <t>0018-Nav</t>
+  </si>
+  <si>
+    <t>0021-Nav</t>
+  </si>
+  <si>
+    <t>0023-Nav</t>
+  </si>
+  <si>
+    <t>0024-Nav</t>
+  </si>
+  <si>
+    <t>0025-Nav</t>
+  </si>
+  <si>
+    <t>0026-Nav</t>
+  </si>
+  <si>
+    <t>0027-Nav</t>
+  </si>
+  <si>
+    <t>0028-Nav</t>
+  </si>
+  <si>
+    <t>0022-Nav</t>
+  </si>
+  <si>
+    <t>6005-RegisterEvent</t>
+  </si>
+  <si>
+    <t>Add lager than available seats and submit form using "Add To My Calendar" button</t>
+  </si>
+  <si>
+    <t>Event Edited in Events</t>
+  </si>
+  <si>
+    <t>Event Edited in Events page</t>
+  </si>
+  <si>
+    <t>Seat Count is limited at seats available</t>
   </si>
 </sst>
 </file>
@@ -354,7 +594,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -370,6 +610,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFA99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,7 +682,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -436,7 +694,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -445,45 +702,43 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7575"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFA99"/>
       <color rgb="FFFF7575"/>
     </mruColors>
   </colors>
@@ -496,6 +751,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -761,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
@@ -809,69 +1068,75 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>30</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="14"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="12"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
@@ -886,13 +1151,13 @@
       <c r="F6" t="s">
         <v>14</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="20" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>20</v>
@@ -909,10 +1174,13 @@
       <c r="F7" t="s">
         <v>14</v>
       </c>
+      <c r="G7" s="20" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>19</v>
@@ -926,10 +1194,16 @@
       <c r="E8" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>162</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>21</v>
@@ -943,10 +1217,16 @@
       <c r="E9" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>22</v>
@@ -960,10 +1240,16 @@
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>164</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>28</v>
@@ -977,10 +1263,16 @@
       <c r="E11" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>165</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>41</v>
@@ -994,10 +1286,16 @@
       <c r="E12" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -1011,24 +1309,30 @@
       <c r="E13" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="14"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="12"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>167</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>20</v>
@@ -1045,10 +1349,13 @@
       <c r="F15" t="s">
         <v>14</v>
       </c>
+      <c r="G15" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>174</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>19</v>
@@ -1062,47 +1369,65 @@
       <c r="E16" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="17" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
+        <v>168</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>81</v>
+        <v>170</v>
+      </c>
+      <c r="B19" t="s">
+        <v>80</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
@@ -1113,10 +1438,16 @@
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="20" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>41</v>
@@ -1130,10 +1461,16 @@
       <c r="E20" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>172</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -1147,37 +1484,49 @@
       <c r="E21" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>173</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
     </row>
     <row r="24" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
@@ -1195,6 +1544,12 @@
       <c r="E24" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="25" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
@@ -1212,6 +1567,12 @@
       <c r="E25" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
@@ -1229,6 +1590,12 @@
       <c r="E26" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
@@ -1246,6 +1613,12 @@
       <c r="E27" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="28" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
@@ -1263,24 +1636,36 @@
       <c r="E28" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
@@ -1298,6 +1683,12 @@
       <c r="E31" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
@@ -1315,6 +1706,12 @@
       <c r="E32" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
@@ -1332,6 +1729,12 @@
       <c r="E33" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
@@ -1349,6 +1752,12 @@
       <c r="E34" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="35" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
@@ -1366,6 +1775,12 @@
       <c r="E35" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="36" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
@@ -1383,6 +1798,12 @@
       <c r="E36" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
@@ -1400,6 +1821,12 @@
       <c r="E37" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
@@ -1417,34 +1844,40 @@
       <c r="E38" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="14"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="12"/>
     </row>
     <row r="41" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
@@ -1462,6 +1895,12 @@
       <c r="E41" s="3" t="s">
         <v>56</v>
       </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="42" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
@@ -1479,6 +1918,12 @@
       <c r="E42" s="3" t="s">
         <v>59</v>
       </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="43" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
@@ -1496,6 +1941,12 @@
       <c r="E43" s="3" t="s">
         <v>62</v>
       </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
@@ -1513,24 +1964,36 @@
       <c r="E44" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
+      <c r="F45" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="14"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="12"/>
     </row>
     <row r="47" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
@@ -1548,6 +2011,12 @@
       <c r="E47" s="3" t="s">
         <v>57</v>
       </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="48" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
@@ -1565,6 +2034,12 @@
       <c r="E48" s="3" t="s">
         <v>67</v>
       </c>
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="49" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
@@ -1582,6 +2057,12 @@
       <c r="E49" s="3" t="s">
         <v>69</v>
       </c>
+      <c r="F49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
@@ -1599,86 +2080,653 @@
       <c r="E50" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="F50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" s="21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A51" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
+      <c r="A51" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" s="6"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
     </row>
     <row r="52" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A53" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
+      <c r="B53" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C53" t="s">
+      <c r="E53" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="F53" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H53" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="I53" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J53" s="14" t="s">
         <v>94</v>
-      </c>
-      <c r="H53" t="s">
-        <v>95</v>
-      </c>
-      <c r="I53" t="s">
-        <v>95</v>
-      </c>
-      <c r="J53" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="57" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
+        <v>95</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="E54" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A55" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C54" t="s">
-        <v>92</v>
-      </c>
-      <c r="D54" s="3" t="s">
+      <c r="B55" s="6"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+    </row>
+    <row r="56" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
         <v>99</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>99</v>
+      <c r="B56" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F56" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>100</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C57" t="s">
+        <v>118</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>101</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C58" t="s">
+        <v>118</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A59" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B59" s="6"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
+    </row>
+    <row r="60" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>107</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" t="s">
+        <v>110</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>114</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C61" t="s">
+        <v>118</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F61" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>115</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C63" t="s">
+        <v>110</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F63" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="F64" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H64" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="I64" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="J64" s="17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A65" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B65" s="6"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="7"/>
+    </row>
+    <row r="66" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>124</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C66" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F66" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>125</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F67" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>120</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F68" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A69" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B69" s="6"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="7"/>
+    </row>
+    <row r="70" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>130</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C70" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F70" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>136</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" t="s">
+        <v>110</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F71" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A72" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B72" s="10"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="12"/>
+    </row>
+    <row r="73" spans="1:10" ht="17.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>137</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C73" t="s">
+        <v>110</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F73" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="17.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>145</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C74" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="F74" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="17.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75" t="s">
+        <v>110</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="F75" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>145</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="F76" t="s">
+        <v>14</v>
+      </c>
+      <c r="G76" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>148</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C77" t="s">
+        <v>110</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="F77" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>153</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="F78" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>156</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="F79" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" s="21" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" display="Go to repo and verify Gituib Actions https://github.com/JeffBolk/QUAL2000-Event-Hub" xr:uid="{32518946-939D-4B73-A67D-34E6923DA913}"/>
+    <hyperlink ref="B6" r:id="rId2" xr:uid="{164CDD4C-78B7-4DD6-BD6D-FE62C562C3F2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/Test-Cases-Submission.xlsx
+++ b/Test-Cases-Submission.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2db921fd99e4e5bb/Documents/St-Lawrence-College/SLC/20252026/Semester 2/QualityAssurance/Final Project/Testing/QUAL2000-Event-Hub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="585" documentId="13_ncr:1_{CC5BAACD-E979-4F94-BEA8-B5AD4B6F2AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0AE8994-4420-4CAB-90CC-4432C7024034}"/>
+  <xr:revisionPtr revIDLastSave="618" documentId="13_ncr:1_{CC5BAACD-E979-4F94-BEA8-B5AD4B6F2AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BBCD289-0FEE-4E49-927E-62429324CDE9}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,9 +69,6 @@
     <t>Click</t>
   </si>
   <si>
-    <t xml:space="preserve">E2E Testing with JS Testing </t>
-  </si>
-  <si>
     <t>1001-Home</t>
   </si>
   <si>
@@ -565,6 +562,9 @@
   </si>
   <si>
     <t>Seat Count is limited at seats available</t>
+  </si>
+  <si>
+    <t>E2E Testing with JS Testing and Playwright</t>
   </si>
 </sst>
 </file>
@@ -682,7 +682,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -708,25 +708,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1028,7 +1019,7 @@
     <col min="3" max="3" width="41.59765625" customWidth="1"/>
     <col min="4" max="4" width="33.46484375" customWidth="1"/>
     <col min="5" max="5" width="33.59765625" customWidth="1"/>
-    <col min="6" max="6" width="29.46484375" customWidth="1"/>
+    <col min="6" max="6" width="35.46484375" customWidth="1"/>
     <col min="7" max="7" width="34.19921875" customWidth="1"/>
     <col min="8" max="8" width="35.06640625" customWidth="1"/>
     <col min="9" max="9" width="34.9296875" customWidth="1"/>
@@ -1069,7 +1060,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
@@ -1083,30 +1074,30 @@
     </row>
     <row r="3" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="7"/>
@@ -1120,7 +1111,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
@@ -1134,7 +1125,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -1149,176 +1140,176 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
@@ -1332,191 +1323,191 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="7"/>
@@ -1530,132 +1521,132 @@
     </row>
     <row r="24" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="7"/>
@@ -1669,191 +1660,191 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C31" t="s">
         <v>13</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C33" t="s">
         <v>13</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G37" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="7"/>
@@ -1867,7 +1858,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
@@ -1881,109 +1872,109 @@
     </row>
     <row r="41" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
         <v>13</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C42" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F42" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G42" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C43" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="E43" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F44" t="s">
-        <v>14</v>
-      </c>
-      <c r="G44" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G44" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" t="s">
-        <v>14</v>
-      </c>
-      <c r="G45" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
@@ -1997,99 +1988,99 @@
     </row>
     <row r="47" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C47" t="s">
         <v>13</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F47" t="s">
-        <v>14</v>
-      </c>
-      <c r="G47" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C48" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="E48" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F48" t="s">
-        <v>14</v>
-      </c>
-      <c r="G48" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G48" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C49" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="E49" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F49" t="s">
-        <v>14</v>
-      </c>
-      <c r="G49" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G49" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C50" t="s">
         <v>13</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F50" t="s">
-        <v>14</v>
-      </c>
-      <c r="G50" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G50" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="7"/>
@@ -2103,85 +2094,85 @@
     </row>
     <row r="52" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F52" t="s">
+        <v>179</v>
+      </c>
+      <c r="G52" s="18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A53" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F52" t="s">
-        <v>14</v>
-      </c>
-      <c r="G52" s="21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A53" s="14" t="s">
+      <c r="B53" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="C53" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D53" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="C53" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="D53" s="15" t="s">
+      <c r="E53" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="E53" s="15" t="s">
+      <c r="F53" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="G53" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H53" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="F53" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G53" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="H53" s="14" t="s">
+      <c r="I53" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="J53" s="13" t="s">
         <v>93</v>
-      </c>
-      <c r="I53" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="J53" s="14" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="57" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" t="s">
+        <v>117</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C54" t="s">
-        <v>118</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="E54" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F54" t="s">
-        <v>14</v>
-      </c>
-      <c r="G54" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G54" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="7"/>
@@ -2195,76 +2186,76 @@
     </row>
     <row r="56" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C56" t="s">
         <v>13</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F56" t="s">
-        <v>14</v>
-      </c>
-      <c r="G56" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G56" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G57" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C58" t="s">
+        <v>117</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C58" t="s">
-        <v>118</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="E58" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F58" t="s">
-        <v>14</v>
-      </c>
-      <c r="G58" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G58" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="7"/>
@@ -2278,131 +2269,131 @@
     </row>
     <row r="60" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60" t="s">
         <v>109</v>
       </c>
-      <c r="C60" t="s">
-        <v>110</v>
-      </c>
       <c r="D60" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F60" t="s">
-        <v>14</v>
-      </c>
-      <c r="G60" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G60" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C61" t="s">
+        <v>117</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C61" t="s">
-        <v>118</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="E61" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F61" t="s">
-        <v>14</v>
-      </c>
-      <c r="G61" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G61" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
+        <v>114</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C62" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="E62" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F62" t="s">
-        <v>14</v>
-      </c>
-      <c r="G62" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G62" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C63" t="s">
+        <v>109</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F63" t="s">
+        <v>179</v>
+      </c>
+      <c r="G63" s="18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B64" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C63" t="s">
-        <v>110</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F63" t="s">
-        <v>14</v>
-      </c>
-      <c r="G63" s="21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="B64" s="18" t="s">
+      <c r="C64" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="C64" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="D64" s="18" t="s">
+      <c r="E64" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="F64" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="G64" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="H64" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="E64" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="F64" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G64" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="H64" s="17" t="s">
+      <c r="I64" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="J64" s="15" t="s">
         <v>143</v>
-      </c>
-      <c r="I64" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="J64" s="17" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="7"/>
@@ -2416,76 +2407,76 @@
     </row>
     <row r="66" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C66" t="s">
         <v>13</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>14</v>
-      </c>
-      <c r="G66" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G66" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C67" t="s">
         <v>13</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F67" t="s">
-        <v>14</v>
-      </c>
-      <c r="G67" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G67" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C68" t="s">
         <v>13</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F68" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G68" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="7"/>
@@ -2499,56 +2490,56 @@
     </row>
     <row r="70" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F70" t="s">
+        <v>179</v>
+      </c>
+      <c r="G70" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" t="s">
         <v>132</v>
-      </c>
-      <c r="C70" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F70" t="s">
-        <v>14</v>
-      </c>
-      <c r="G70" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J70" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C71" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F71" t="s">
-        <v>14</v>
-      </c>
-      <c r="G71" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G71" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B72" s="10"/>
       <c r="C72" s="11"/>
@@ -2562,163 +2553,163 @@
     </row>
     <row r="73" spans="1:10" ht="17.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
+        <v>136</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="C73" t="s">
+        <v>109</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C73" t="s">
-        <v>110</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E73" s="13" t="s">
-        <v>139</v>
+      <c r="E73" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="F73" t="s">
-        <v>14</v>
-      </c>
-      <c r="G73" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G73" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="17.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
+        <v>144</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C74" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C74" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="E74" s="13" t="s">
-        <v>146</v>
+      <c r="E74" s="3" t="s">
+        <v>145</v>
       </c>
       <c r="F74" t="s">
-        <v>14</v>
-      </c>
-      <c r="G74" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G74" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="17.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
+        <v>147</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="C75" t="s">
-        <v>110</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="E75" s="13" t="s">
-        <v>177</v>
+        <v>109</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="F75" t="s">
-        <v>14</v>
-      </c>
-      <c r="G75" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G75" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C76" t="s">
         <v>13</v>
       </c>
-      <c r="D76" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>152</v>
+      <c r="D76" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>151</v>
       </c>
       <c r="F76" t="s">
-        <v>14</v>
-      </c>
-      <c r="G76" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G76" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C77" t="s">
-        <v>110</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>178</v>
+        <v>109</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="F77" t="s">
-        <v>14</v>
-      </c>
-      <c r="G77" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G77" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
+        <v>152</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C78" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="E78" s="13" t="s">
-        <v>155</v>
+      <c r="E78" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="F78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G78" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G78" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C79" t="s">
-        <v>13</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="E79" s="13" t="s">
-        <v>158</v>
+      <c r="E79" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="F79" t="s">
-        <v>14</v>
-      </c>
-      <c r="G79" s="21" t="s">
-        <v>18</v>
+        <v>179</v>
+      </c>
+      <c r="G79" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
